--- a/table/Datas/#KnockbackConfig.xlsx
+++ b/table/Datas/#KnockbackConfig.xlsx
@@ -590,7 +590,7 @@
         <v>6.2</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>17</v>

--- a/table/Datas/#KnockbackConfig.xlsx
+++ b/table/Datas/#KnockbackConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,91 @@
           <t>spawn_radius</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>shot_speed</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>shot_range</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>shot_radius</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>hit_radius</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ammo_max</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>reload_seconds</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>fire_cooldown_seconds</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>recoil</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>damage_per_hit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>knockback_base</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>knockback_scale</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>knockback_carry</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>stun_base</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>stun_scale</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>stun_gain</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>body_restitution</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>zone_first_reveal_seconds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +604,91 @@
           <t>float</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -576,6 +746,91 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>spawn_radius</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>shot_speed</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>shot_range</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>shot_radius</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>hit_radius</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ammo_max</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>reload_seconds</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>fire_cooldown_seconds</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>recoil</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>damage_per_hit</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>knockback_base</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>knockback_scale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>knockback_carry</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>stun_base</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>stun_scale</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>stun_gain</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>body_restitution</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>zone_first_reveal_seconds</t>
         </is>
       </c>
     </row>
@@ -606,6 +861,57 @@
       </c>
       <c r="J5" t="n">
         <v>11</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#KnockbackConfig.xlsx
+++ b/table/Datas/#KnockbackConfig.xlsx
@@ -413,8 +413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -552,6 +559,26 @@
           <t>zone_first_reveal_seconds</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pillar_count</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>pillar_ring_radius</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>pillar_radius</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>pillar_height</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -689,6 +716,26 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -831,6 +878,26 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>zone_first_reveal_seconds</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>pillar_count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>pillar_ring_radius</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>pillar_radius</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>pillar_height</t>
         </is>
       </c>
     </row>
@@ -912,6 +979,18 @@
       </c>
       <c r="AA5" t="n">
         <v>8</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
